--- a/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1427"/>
+  <dimension ref="A1:C1430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21916,6 +21916,51 @@
         <v>200</v>
       </c>
     </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>CKCtVmJf</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>CKCtVmJf</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1430"/>
+  <dimension ref="A1:C1431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21961,6 +21961,21 @@
         <v>201</v>
       </c>
     </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>202</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1431"/>
+  <dimension ref="A1:C1432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21976,6 +21976,21 @@
         <v>202</v>
       </c>
     </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>KIxd2dNg</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1432"/>
+  <dimension ref="A1:C1433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21991,6 +21991,22 @@
         <v>203</v>
       </c>
     </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso t 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1433"/>
+  <dimension ref="A1:C1434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22007,6 +22007,21 @@
         <v>177</v>
       </c>
     </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
